--- a/tabla_embalajes.xlsx
+++ b/tabla_embalajes.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Fer\IA\01 Optimización de cargas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0D50EC5-885F-48E2-8F4E-25A7D593723A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD358744-0BF1-4E97-A678-613DEA5A7102}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="211" uniqueCount="156">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="167">
   <si>
     <t>DUNS Proveedor</t>
   </si>
@@ -491,13 +491,46 @@
   </si>
   <si>
     <t>PN-100</t>
+  </si>
+  <si>
+    <t>EMB-99</t>
+  </si>
+  <si>
+    <t>PN-997</t>
+  </si>
+  <si>
+    <t>PN-998</t>
+  </si>
+  <si>
+    <t>PN-987</t>
+  </si>
+  <si>
+    <t>PN-991</t>
+  </si>
+  <si>
+    <t>PN-992</t>
+  </si>
+  <si>
+    <t>EMB-96</t>
+  </si>
+  <si>
+    <t>EMB-97</t>
+  </si>
+  <si>
+    <t>EMB-98</t>
+  </si>
+  <si>
+    <t>EMB-95</t>
+  </si>
+  <si>
+    <t>Prioridad de carga</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -514,6 +547,12 @@
     <font>
       <sz val="10"/>
       <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="4">
@@ -874,17 +913,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G103"/>
+  <dimension ref="A1:H108"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
     <col min="2" max="2" width="14" customWidth="1"/>
     <col min="3" max="3" width="10" customWidth="1"/>
     <col min="4" max="6" width="20" customWidth="1"/>
-    <col min="7" max="7" width="22" customWidth="1"/>
+    <col min="7" max="8" width="22" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -906,8 +945,11 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H1" s="1" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="2">
         <v>111000001</v>
       </c>
@@ -929,8 +971,9 @@
       <c r="G2" s="2">
         <v>10</v>
       </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H2" s="2"/>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="3">
         <v>111000001</v>
       </c>
@@ -952,8 +995,9 @@
       <c r="G3" s="3">
         <v>4</v>
       </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H3" s="3"/>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
         <v>111000001</v>
       </c>
@@ -975,8 +1019,9 @@
       <c r="G4" s="2">
         <v>8</v>
       </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H4" s="2"/>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="3">
         <v>111000001</v>
       </c>
@@ -998,8 +1043,9 @@
       <c r="G5" s="3">
         <v>4</v>
       </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H5" s="3"/>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
         <v>111000001</v>
       </c>
@@ -1021,8 +1067,9 @@
       <c r="G6" s="2">
         <v>10</v>
       </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H6" s="2"/>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="3">
         <v>222000002</v>
       </c>
@@ -1044,8 +1091,9 @@
       <c r="G7" s="3">
         <v>6</v>
       </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H7" s="3"/>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
         <v>222000002</v>
       </c>
@@ -1067,8 +1115,9 @@
       <c r="G8" s="2">
         <v>12</v>
       </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H8" s="2"/>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="3">
         <v>222000002</v>
       </c>
@@ -1090,8 +1139,9 @@
       <c r="G9" s="3">
         <v>10</v>
       </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H9" s="3"/>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
         <v>222000002</v>
       </c>
@@ -1113,8 +1163,9 @@
       <c r="G10" s="2">
         <v>6</v>
       </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H10" s="2"/>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="3">
         <v>222000002</v>
       </c>
@@ -1136,8 +1187,9 @@
       <c r="G11" s="3">
         <v>10</v>
       </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H11" s="3"/>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" s="2">
         <v>333000003</v>
       </c>
@@ -1159,8 +1211,9 @@
       <c r="G12" s="2">
         <v>5</v>
       </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H12" s="2"/>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="3">
         <v>333000003</v>
       </c>
@@ -1182,8 +1235,9 @@
       <c r="G13" s="3">
         <v>12</v>
       </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H13" s="3"/>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" s="2">
         <v>333000003</v>
       </c>
@@ -1205,8 +1259,9 @@
       <c r="G14" s="2">
         <v>4</v>
       </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H14" s="2"/>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" s="3">
         <v>333000003</v>
       </c>
@@ -1228,8 +1283,9 @@
       <c r="G15" s="3">
         <v>4</v>
       </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H15" s="3"/>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" s="2">
         <v>333000003</v>
       </c>
@@ -1251,8 +1307,9 @@
       <c r="G16" s="2">
         <v>12</v>
       </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H16" s="2"/>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" s="3">
         <v>444000004</v>
       </c>
@@ -1274,8 +1331,9 @@
       <c r="G17" s="3">
         <v>5</v>
       </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H17" s="3"/>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" s="2">
         <v>444000004</v>
       </c>
@@ -1297,8 +1355,9 @@
       <c r="G18" s="2">
         <v>6</v>
       </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H18" s="2"/>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="3">
         <v>444000004</v>
       </c>
@@ -1320,8 +1379,9 @@
       <c r="G19" s="3">
         <v>4</v>
       </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H19" s="3"/>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" s="2">
         <v>444000004</v>
       </c>
@@ -1343,8 +1403,9 @@
       <c r="G20" s="2">
         <v>5</v>
       </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H20" s="2"/>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="3">
         <v>444000004</v>
       </c>
@@ -1366,8 +1427,9 @@
       <c r="G21" s="3">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H21" s="3"/>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" s="2">
         <v>555000005</v>
       </c>
@@ -1389,8 +1451,9 @@
       <c r="G22" s="2">
         <v>8</v>
       </c>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H22" s="2"/>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" s="3">
         <v>555000005</v>
       </c>
@@ -1412,8 +1475,9 @@
       <c r="G23" s="3">
         <v>6</v>
       </c>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H23" s="3"/>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" s="2">
         <v>555000005</v>
       </c>
@@ -1435,8 +1499,9 @@
       <c r="G24" s="2">
         <v>8</v>
       </c>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H24" s="2"/>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" s="3">
         <v>555000005</v>
       </c>
@@ -1458,8 +1523,9 @@
       <c r="G25" s="3">
         <v>12</v>
       </c>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H25" s="3"/>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" s="2">
         <v>555000005</v>
       </c>
@@ -1481,8 +1547,9 @@
       <c r="G26" s="2">
         <v>6</v>
       </c>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H26" s="2"/>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" s="3">
         <v>666000006</v>
       </c>
@@ -1504,8 +1571,9 @@
       <c r="G27" s="3">
         <v>5</v>
       </c>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H27" s="3"/>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" s="2">
         <v>666000006</v>
       </c>
@@ -1527,8 +1595,9 @@
       <c r="G28" s="2">
         <v>6</v>
       </c>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H28" s="2"/>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" s="3">
         <v>666000006</v>
       </c>
@@ -1550,8 +1619,9 @@
       <c r="G29" s="3">
         <v>6</v>
       </c>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H29" s="3"/>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" s="2">
         <v>666000006</v>
       </c>
@@ -1573,8 +1643,9 @@
       <c r="G30" s="2">
         <v>5</v>
       </c>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H30" s="2"/>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" s="3">
         <v>666000006</v>
       </c>
@@ -1596,8 +1667,9 @@
       <c r="G31" s="3">
         <v>12</v>
       </c>
-    </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H31" s="3"/>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" s="2">
         <v>777000007</v>
       </c>
@@ -1619,8 +1691,9 @@
       <c r="G32" s="2">
         <v>6</v>
       </c>
-    </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H32" s="2"/>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" s="3">
         <v>777000007</v>
       </c>
@@ -1642,8 +1715,9 @@
       <c r="G33" s="3">
         <v>12</v>
       </c>
-    </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H33" s="3"/>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" s="2">
         <v>777000007</v>
       </c>
@@ -1665,8 +1739,9 @@
       <c r="G34" s="2">
         <v>12</v>
       </c>
-    </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H34" s="2"/>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" s="3">
         <v>777000007</v>
       </c>
@@ -1688,8 +1763,9 @@
       <c r="G35" s="3">
         <v>12</v>
       </c>
-    </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H35" s="3"/>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" s="2">
         <v>777000007</v>
       </c>
@@ -1711,8 +1787,9 @@
       <c r="G36" s="2">
         <v>4</v>
       </c>
-    </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H36" s="2"/>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" s="3">
         <v>888000008</v>
       </c>
@@ -1734,8 +1811,9 @@
       <c r="G37" s="3">
         <v>10</v>
       </c>
-    </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H37" s="3"/>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" s="2">
         <v>888000008</v>
       </c>
@@ -1757,8 +1835,9 @@
       <c r="G38" s="2">
         <v>12</v>
       </c>
-    </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H38" s="2"/>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" s="3">
         <v>888000008</v>
       </c>
@@ -1780,8 +1859,9 @@
       <c r="G39" s="3">
         <v>5</v>
       </c>
-    </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H39" s="3"/>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" s="2">
         <v>888000008</v>
       </c>
@@ -1803,8 +1883,9 @@
       <c r="G40" s="2">
         <v>10</v>
       </c>
-    </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H40" s="2"/>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" s="3">
         <v>888000008</v>
       </c>
@@ -1826,8 +1907,9 @@
       <c r="G41" s="3">
         <v>12</v>
       </c>
-    </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H41" s="3"/>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" s="2">
         <v>999000009</v>
       </c>
@@ -1849,8 +1931,9 @@
       <c r="G42" s="2">
         <v>5</v>
       </c>
-    </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H42" s="2"/>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" s="3">
         <v>999000009</v>
       </c>
@@ -1872,8 +1955,9 @@
       <c r="G43" s="3">
         <v>5</v>
       </c>
-    </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H43" s="3"/>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44" s="2">
         <v>999000009</v>
       </c>
@@ -1895,8 +1979,9 @@
       <c r="G44" s="2">
         <v>8</v>
       </c>
-    </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H44" s="2"/>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45" s="3">
         <v>999000009</v>
       </c>
@@ -1918,8 +2003,9 @@
       <c r="G45" s="3">
         <v>8</v>
       </c>
-    </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H45" s="3"/>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A46" s="2">
         <v>999000009</v>
       </c>
@@ -1941,8 +2027,9 @@
       <c r="G46" s="2">
         <v>6</v>
       </c>
-    </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H46" s="2"/>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A47" s="3">
         <v>101000010</v>
       </c>
@@ -1964,8 +2051,9 @@
       <c r="G47" s="3">
         <v>12</v>
       </c>
-    </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H47" s="3"/>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A48" s="2">
         <v>101000010</v>
       </c>
@@ -1987,8 +2075,9 @@
       <c r="G48" s="2">
         <v>12</v>
       </c>
-    </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H48" s="2"/>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A49" s="3">
         <v>101000010</v>
       </c>
@@ -2010,8 +2099,9 @@
       <c r="G49" s="3">
         <v>10</v>
       </c>
-    </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H49" s="3"/>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A50" s="2">
         <v>101000010</v>
       </c>
@@ -2033,8 +2123,9 @@
       <c r="G50" s="2">
         <v>5</v>
       </c>
-    </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H50" s="2"/>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A51" s="3">
         <v>101000010</v>
       </c>
@@ -2056,8 +2147,9 @@
       <c r="G51" s="3">
         <v>12</v>
       </c>
-    </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H51" s="3"/>
+    </row>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A52" s="2">
         <v>111000001</v>
       </c>
@@ -2079,8 +2171,9 @@
       <c r="G52" s="2">
         <v>5</v>
       </c>
-    </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H52" s="2"/>
+    </row>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A53" s="3">
         <v>111000001</v>
       </c>
@@ -2102,8 +2195,9 @@
       <c r="G53" s="3">
         <v>5</v>
       </c>
-    </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H53" s="3"/>
+    </row>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A54" s="2">
         <v>222000002</v>
       </c>
@@ -2125,8 +2219,9 @@
       <c r="G54" s="2">
         <v>4</v>
       </c>
-    </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H54" s="2"/>
+    </row>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A55" s="3">
         <v>222000002</v>
       </c>
@@ -2148,8 +2243,9 @@
       <c r="G55" s="3">
         <v>8</v>
       </c>
-    </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H55" s="3"/>
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A56" s="2">
         <v>333000003</v>
       </c>
@@ -2171,8 +2267,9 @@
       <c r="G56" s="2">
         <v>12</v>
       </c>
-    </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H56" s="2"/>
+    </row>
+    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A57" s="3">
         <v>333000003</v>
       </c>
@@ -2194,8 +2291,9 @@
       <c r="G57" s="3">
         <v>10</v>
       </c>
-    </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H57" s="3"/>
+    </row>
+    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A58" s="2">
         <v>444000004</v>
       </c>
@@ -2217,8 +2315,9 @@
       <c r="G58" s="2">
         <v>8</v>
       </c>
-    </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H58" s="2"/>
+    </row>
+    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A59" s="3">
         <v>444000004</v>
       </c>
@@ -2240,8 +2339,9 @@
       <c r="G59" s="3">
         <v>10</v>
       </c>
-    </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H59" s="3"/>
+    </row>
+    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A60" s="2">
         <v>555000005</v>
       </c>
@@ -2263,8 +2363,9 @@
       <c r="G60" s="2">
         <v>8</v>
       </c>
-    </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H60" s="2"/>
+    </row>
+    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A61" s="3">
         <v>555000005</v>
       </c>
@@ -2286,8 +2387,9 @@
       <c r="G61" s="3">
         <v>5</v>
       </c>
-    </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H61" s="3"/>
+    </row>
+    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A62" s="2">
         <v>666000006</v>
       </c>
@@ -2309,8 +2411,9 @@
       <c r="G62" s="2">
         <v>12</v>
       </c>
-    </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H62" s="2"/>
+    </row>
+    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A63" s="3">
         <v>666000006</v>
       </c>
@@ -2332,8 +2435,9 @@
       <c r="G63" s="3">
         <v>6</v>
       </c>
-    </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H63" s="3"/>
+    </row>
+    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A64" s="2">
         <v>777000007</v>
       </c>
@@ -2355,8 +2459,9 @@
       <c r="G64" s="2">
         <v>10</v>
       </c>
-    </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H64" s="2"/>
+    </row>
+    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A65" s="3">
         <v>777000007</v>
       </c>
@@ -2378,8 +2483,9 @@
       <c r="G65" s="3">
         <v>4</v>
       </c>
-    </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H65" s="3"/>
+    </row>
+    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A66" s="2">
         <v>888000008</v>
       </c>
@@ -2401,8 +2507,9 @@
       <c r="G66" s="2">
         <v>8</v>
       </c>
-    </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H66" s="2"/>
+    </row>
+    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A67" s="3">
         <v>888000008</v>
       </c>
@@ -2424,8 +2531,9 @@
       <c r="G67" s="3">
         <v>10</v>
       </c>
-    </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H67" s="3"/>
+    </row>
+    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A68" s="2">
         <v>999000009</v>
       </c>
@@ -2447,8 +2555,9 @@
       <c r="G68" s="2">
         <v>5</v>
       </c>
-    </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H68" s="2"/>
+    </row>
+    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A69" s="3">
         <v>999000009</v>
       </c>
@@ -2470,8 +2579,9 @@
       <c r="G69" s="3">
         <v>4</v>
       </c>
-    </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H69" s="3"/>
+    </row>
+    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A70" s="2">
         <v>101000010</v>
       </c>
@@ -2493,8 +2603,9 @@
       <c r="G70" s="2">
         <v>5</v>
       </c>
-    </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H70" s="2"/>
+    </row>
+    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A71" s="3">
         <v>101000010</v>
       </c>
@@ -2516,8 +2627,9 @@
       <c r="G71" s="3">
         <v>4</v>
       </c>
-    </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H71" s="3"/>
+    </row>
+    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A72" s="2">
         <v>112000011</v>
       </c>
@@ -2539,8 +2651,9 @@
       <c r="G72" s="2">
         <v>5</v>
       </c>
-    </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H72" s="2"/>
+    </row>
+    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A73" s="3">
         <v>112000011</v>
       </c>
@@ -2562,8 +2675,9 @@
       <c r="G73" s="3">
         <v>12</v>
       </c>
-    </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H73" s="3"/>
+    </row>
+    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A74" s="2">
         <v>112000011</v>
       </c>
@@ -2585,8 +2699,9 @@
       <c r="G74" s="2">
         <v>10</v>
       </c>
-    </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H74" s="2"/>
+    </row>
+    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A75" s="3">
         <v>223000012</v>
       </c>
@@ -2608,8 +2723,9 @@
       <c r="G75" s="3">
         <v>12</v>
       </c>
-    </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H75" s="3"/>
+    </row>
+    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A76" s="2">
         <v>223000012</v>
       </c>
@@ -2631,8 +2747,9 @@
       <c r="G76" s="2">
         <v>4</v>
       </c>
-    </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H76" s="2"/>
+    </row>
+    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A77" s="3">
         <v>223000012</v>
       </c>
@@ -2654,8 +2771,9 @@
       <c r="G77" s="3">
         <v>8</v>
       </c>
-    </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H77" s="3"/>
+    </row>
+    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A78" s="2">
         <v>334000013</v>
       </c>
@@ -2677,8 +2795,9 @@
       <c r="G78" s="2">
         <v>4</v>
       </c>
-    </row>
-    <row r="79" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H78" s="2"/>
+    </row>
+    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A79" s="3">
         <v>334000013</v>
       </c>
@@ -2700,8 +2819,9 @@
       <c r="G79" s="3">
         <v>4</v>
       </c>
-    </row>
-    <row r="80" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H79" s="3"/>
+    </row>
+    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A80" s="2">
         <v>334000013</v>
       </c>
@@ -2723,8 +2843,9 @@
       <c r="G80" s="2">
         <v>10</v>
       </c>
-    </row>
-    <row r="81" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H80" s="2"/>
+    </row>
+    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A81" s="3">
         <v>445000014</v>
       </c>
@@ -2746,8 +2867,9 @@
       <c r="G81" s="3">
         <v>6</v>
       </c>
-    </row>
-    <row r="82" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H81" s="3"/>
+    </row>
+    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A82" s="2">
         <v>445000014</v>
       </c>
@@ -2769,8 +2891,9 @@
       <c r="G82" s="2">
         <v>8</v>
       </c>
-    </row>
-    <row r="83" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H82" s="2"/>
+    </row>
+    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A83" s="3">
         <v>445000014</v>
       </c>
@@ -2792,8 +2915,9 @@
       <c r="G83" s="3">
         <v>12</v>
       </c>
-    </row>
-    <row r="84" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H83" s="3"/>
+    </row>
+    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A84" s="2">
         <v>556000015</v>
       </c>
@@ -2815,8 +2939,9 @@
       <c r="G84" s="2">
         <v>6</v>
       </c>
-    </row>
-    <row r="85" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H84" s="2"/>
+    </row>
+    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A85" s="3">
         <v>556000015</v>
       </c>
@@ -2838,8 +2963,9 @@
       <c r="G85" s="3">
         <v>5</v>
       </c>
-    </row>
-    <row r="86" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H85" s="3"/>
+    </row>
+    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A86" s="2">
         <v>556000015</v>
       </c>
@@ -2861,8 +2987,9 @@
       <c r="G86" s="2">
         <v>8</v>
       </c>
-    </row>
-    <row r="87" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H86" s="2"/>
+    </row>
+    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A87" s="3">
         <v>667000016</v>
       </c>
@@ -2884,8 +3011,9 @@
       <c r="G87" s="3">
         <v>12</v>
       </c>
-    </row>
-    <row r="88" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H87" s="3"/>
+    </row>
+    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A88" s="2">
         <v>667000016</v>
       </c>
@@ -2907,8 +3035,9 @@
       <c r="G88" s="2">
         <v>10</v>
       </c>
-    </row>
-    <row r="89" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H88" s="2"/>
+    </row>
+    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A89" s="3">
         <v>667000016</v>
       </c>
@@ -2930,8 +3059,9 @@
       <c r="G89" s="3">
         <v>5</v>
       </c>
-    </row>
-    <row r="90" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H89" s="3"/>
+    </row>
+    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A90" s="2">
         <v>778000017</v>
       </c>
@@ -2953,8 +3083,9 @@
       <c r="G90" s="2">
         <v>4</v>
       </c>
-    </row>
-    <row r="91" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H90" s="2"/>
+    </row>
+    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A91" s="3">
         <v>778000017</v>
       </c>
@@ -2976,8 +3107,9 @@
       <c r="G91" s="3">
         <v>5</v>
       </c>
-    </row>
-    <row r="92" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H91" s="3"/>
+    </row>
+    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A92" s="2">
         <v>778000017</v>
       </c>
@@ -2999,8 +3131,9 @@
       <c r="G92" s="2">
         <v>5</v>
       </c>
-    </row>
-    <row r="93" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H92" s="2"/>
+    </row>
+    <row r="93" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A93" s="3">
         <v>889000018</v>
       </c>
@@ -3022,8 +3155,9 @@
       <c r="G93" s="3">
         <v>5</v>
       </c>
-    </row>
-    <row r="94" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H93" s="3"/>
+    </row>
+    <row r="94" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A94" s="2">
         <v>889000018</v>
       </c>
@@ -3045,8 +3179,9 @@
       <c r="G94" s="2">
         <v>6</v>
       </c>
-    </row>
-    <row r="95" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H94" s="2"/>
+    </row>
+    <row r="95" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A95" s="3">
         <v>889000018</v>
       </c>
@@ -3068,8 +3203,9 @@
       <c r="G95" s="3">
         <v>5</v>
       </c>
-    </row>
-    <row r="96" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H95" s="3"/>
+    </row>
+    <row r="96" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A96" s="2">
         <v>990000019</v>
       </c>
@@ -3091,8 +3227,9 @@
       <c r="G96" s="2">
         <v>4</v>
       </c>
-    </row>
-    <row r="97" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H96" s="2"/>
+    </row>
+    <row r="97" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A97" s="3">
         <v>990000019</v>
       </c>
@@ -3114,8 +3251,9 @@
       <c r="G97" s="3">
         <v>5</v>
       </c>
-    </row>
-    <row r="98" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H97" s="3"/>
+    </row>
+    <row r="98" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A98" s="2">
         <v>990000019</v>
       </c>
@@ -3137,8 +3275,9 @@
       <c r="G98" s="2">
         <v>10</v>
       </c>
-    </row>
-    <row r="99" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H98" s="2"/>
+    </row>
+    <row r="99" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A99" s="3">
         <v>100100020</v>
       </c>
@@ -3160,8 +3299,9 @@
       <c r="G99" s="3">
         <v>10</v>
       </c>
-    </row>
-    <row r="100" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H99" s="3"/>
+    </row>
+    <row r="100" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A100" s="2">
         <v>100100020</v>
       </c>
@@ -3183,8 +3323,9 @@
       <c r="G100" s="2">
         <v>6</v>
       </c>
-    </row>
-    <row r="101" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H100" s="2"/>
+    </row>
+    <row r="101" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A101" s="3">
         <v>100100020</v>
       </c>
@@ -3206,8 +3347,9 @@
       <c r="G101" s="3">
         <v>8</v>
       </c>
-    </row>
-    <row r="102" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H101" s="3"/>
+    </row>
+    <row r="102" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A102" s="2">
         <v>999000009</v>
       </c>
@@ -3229,8 +3371,9 @@
       <c r="G102" s="2">
         <v>10</v>
       </c>
-    </row>
-    <row r="103" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H102" s="2"/>
+    </row>
+    <row r="103" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A103" s="3">
         <v>999000009</v>
       </c>
@@ -3252,9 +3395,135 @@
       <c r="G103" s="3">
         <v>7</v>
       </c>
+      <c r="H103" s="3"/>
+    </row>
+    <row r="104" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A104" s="2">
+        <v>990000019</v>
+      </c>
+      <c r="B104" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="C104" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="D104" s="2">
+        <v>260</v>
+      </c>
+      <c r="E104" s="2">
+        <v>100</v>
+      </c>
+      <c r="F104" s="2">
+        <v>85</v>
+      </c>
+      <c r="G104" s="2">
+        <v>1</v>
+      </c>
+      <c r="H104" s="2"/>
+    </row>
+    <row r="105" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A105" s="3">
+        <v>990000019</v>
+      </c>
+      <c r="B105" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="C105" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="D105" s="3">
+        <v>260</v>
+      </c>
+      <c r="E105" s="3">
+        <v>100</v>
+      </c>
+      <c r="F105" s="3">
+        <v>85</v>
+      </c>
+      <c r="G105" s="3">
+        <v>1</v>
+      </c>
+      <c r="H105" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="106" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A106" s="2">
+        <v>990000019</v>
+      </c>
+      <c r="B106" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="C106" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="D106" s="2">
+        <v>260</v>
+      </c>
+      <c r="E106" s="2">
+        <v>100</v>
+      </c>
+      <c r="F106" s="2">
+        <v>85</v>
+      </c>
+      <c r="G106" s="2">
+        <v>1</v>
+      </c>
+      <c r="H106" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="107" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A107" s="3">
+        <v>999000009</v>
+      </c>
+      <c r="B107" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="C107" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="D107" s="3">
+        <v>260</v>
+      </c>
+      <c r="E107" s="3">
+        <v>100</v>
+      </c>
+      <c r="F107" s="3">
+        <v>85</v>
+      </c>
+      <c r="G107" s="3">
+        <v>1</v>
+      </c>
+      <c r="H107" s="3"/>
+    </row>
+    <row r="108" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A108" s="2">
+        <v>999000009</v>
+      </c>
+      <c r="B108" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="C108" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="D108" s="2">
+        <v>260</v>
+      </c>
+      <c r="E108" s="2">
+        <v>100</v>
+      </c>
+      <c r="F108" s="2">
+        <v>85</v>
+      </c>
+      <c r="G108" s="2">
+        <v>1</v>
+      </c>
+      <c r="H108" s="2"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:G101" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>